--- a/demo-data/olivine_demo_transport_cost_overview.xlsx
+++ b/demo-data/olivine_demo_transport_cost_overview.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                   (set the period-month picker to 2026-10 first)</t>
+          <t xml:space="preserve">                                   (set the period-month picker to 2026-09 first)</t>
         </is>
       </c>
     </row>
@@ -528,33 +528,71 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>All data below is SYNTHETIC -- generated for this demonstration,</t>
+          <t>Dates run 1 Aug - 28 Sep 2026 (today), with explicit rows on Today</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>not Olivine's real historical or October 2026 operating data.</t>
+          <t>and Yesterday, so the Command Centre's default filters (Today,</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>See DEMO_DATA_README.md for the full walkthrough, including the</t>
+          <t>Yesterday, This week, This month, Previous month) all show real</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>multi-load and Add-New demo steps that can't be shown via a bulk</t>
+          <t>data immediately after import -- no need to switch to a custom</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
+        <is>
+          <t>range for the demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>All data below is SYNTHETIC -- generated for this demonstration,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>not Olivine's real historical operating data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>See DEMO_DATA_README.md for the full walkthrough, including the</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>multi-load and Add-New demo steps that can't be shown via a bulk</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>file upload.</t>
         </is>
@@ -571,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -635,7 +673,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08.10.26</t>
+          <t>27.09.26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -659,7 +697,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6681</v>
+        <v>4407</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -672,13 +710,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>585.11</v>
+        <v>465.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11.10.26</t>
+          <t>05.09.26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -702,7 +740,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7561</v>
+        <v>9632</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -715,13 +753,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>308.81</v>
+        <v>412.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12.10.26</t>
+          <t>24.09.26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -745,7 +783,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>16773</v>
+        <v>15227</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -758,13 +796,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>203.79</v>
+        <v>552.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>17.10.26</t>
+          <t>14.09.26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -788,7 +826,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4361</v>
+        <v>16956</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -801,13 +839,13 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>219.36</v>
+        <v>122.33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19.10.26</t>
+          <t>28.09.26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -831,7 +869,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>11690</v>
+        <v>6636</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -844,13 +882,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>509.14</v>
+        <v>241.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23.10.26</t>
+          <t>18.09.26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,7 +912,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10718</v>
+        <v>4350</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -887,13 +925,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>193.66</v>
+        <v>359.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>21.10.26</t>
+          <t>28.09.26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -917,7 +955,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>9435</v>
+        <v>12235</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -930,13 +968,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>479.54</v>
+        <v>251.49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13.10.26</t>
+          <t>03.08.26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -960,7 +998,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>14217</v>
+        <v>8699</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -973,13 +1011,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>341.74</v>
+        <v>439.17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>04.10.26</t>
+          <t>23.09.26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1003,7 +1041,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12285</v>
+        <v>15985</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1016,13 +1054,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>363.14</v>
+        <v>612.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20.10.26</t>
+          <t>07.08.26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1046,7 +1084,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5508</v>
+        <v>7078</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1059,13 +1097,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>469.11</v>
+        <v>545.8099999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05.10.26</t>
+          <t>28.09.26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1089,7 +1127,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10915</v>
+        <v>7373</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1102,13 +1140,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>649.52</v>
+        <v>527.5599999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07.10.26</t>
+          <t>29.08.26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1132,7 +1170,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9927</v>
+        <v>8980</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1145,13 +1183,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>189.43</v>
+        <v>328.15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>24.10.26</t>
+          <t>24.09.26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1175,7 +1213,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>14205</v>
+        <v>14841</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1188,13 +1226,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>249.53</v>
+        <v>95.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>03.10.26</t>
+          <t>28.09.26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1218,7 +1256,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>10795</v>
+        <v>15005</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1231,13 +1269,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>99.11</v>
+        <v>551.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>22.10.26</t>
+          <t>26.09.26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1261,7 +1299,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>16542</v>
+        <v>13351</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1274,13 +1312,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>406.44</v>
+        <v>284.94</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05.10.26</t>
+          <t>13.08.26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1304,7 +1342,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>10136</v>
+        <v>11096</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1317,13 +1355,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>465.72</v>
+        <v>468.29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02.10.26</t>
+          <t>27.09.26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1347,7 +1385,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>16200</v>
+        <v>14925</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1360,13 +1398,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>343.05</v>
+        <v>220.63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06.10.26</t>
+          <t>22.08.26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1390,7 +1428,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10634</v>
+        <v>14976</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1403,13 +1441,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>638.95</v>
+        <v>226.11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>15.10.26</t>
+          <t>26.09.26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1433,7 +1471,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>12148</v>
+        <v>4009</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1446,13 +1484,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>228.44</v>
+        <v>357.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13.10.26</t>
+          <t>22.09.26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1476,7 +1514,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6680</v>
+        <v>14179</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1489,13 +1527,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>207.17</v>
+        <v>496.86</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07.10.26</t>
+          <t>22.09.26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1519,7 +1557,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11966</v>
+        <v>9909</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1532,13 +1570,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>515.1</v>
+        <v>99.15000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>11.10.26</t>
+          <t>30.08.26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1562,7 +1600,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>10133</v>
+        <v>14124</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1575,13 +1613,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>154.32</v>
+        <v>140.63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06.10.26</t>
+          <t>26.09.26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1624,7 +1662,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06.10.26</t>
+          <t>26.09.26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1667,7 +1705,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>12.10.26</t>
+          <t>25.09.26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1702,6 +1740,135 @@
         <is>
           <t>Bulawayo</t>
         </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>28.09.26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Hypery</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bakers Inn Bakeries</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ZEE TRUCKING</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>INV-9100</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>9200</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ABC7788</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Harare</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>28.09.26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Olivine</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brainscope</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SIGHTSCORE</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>INV-9101</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>5400</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>AGL8230</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Gweru</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>265.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>27.09.26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Surface</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Kingy Wholesalers</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NORTHLAND</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>INV-9102</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>7100</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>AGJ7091</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Masvingo</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>410.75</v>
       </c>
     </row>
   </sheetData>
@@ -1715,7 +1882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1785,7 +1952,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1814,22 +1981,22 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2316</v>
+        <v>785</v>
       </c>
       <c r="H2" t="n">
-        <v>2871.53</v>
+        <v>6614.64</v>
       </c>
       <c r="I2" t="n">
-        <v>430.73</v>
+        <v>992.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3302.26</v>
+        <v>7606.84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1858,22 +2025,22 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1701</v>
+        <v>2976</v>
       </c>
       <c r="H3" t="n">
-        <v>6283.03</v>
+        <v>2618.56</v>
       </c>
       <c r="I3" t="n">
-        <v>942.45</v>
+        <v>392.78</v>
       </c>
       <c r="J3" t="n">
-        <v>7225.48</v>
+        <v>3011.34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1902,22 +2069,22 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2566</v>
+        <v>2589</v>
       </c>
       <c r="H4" t="n">
-        <v>2419.85</v>
+        <v>3155.52</v>
       </c>
       <c r="I4" t="n">
-        <v>362.98</v>
+        <v>473.33</v>
       </c>
       <c r="J4" t="n">
-        <v>2782.83</v>
+        <v>3628.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1946,22 +2113,22 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>648</v>
+        <v>544</v>
       </c>
       <c r="H5" t="n">
-        <v>3246.79</v>
+        <v>5650.03</v>
       </c>
       <c r="I5" t="n">
-        <v>487.02</v>
+        <v>847.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3733.81</v>
+        <v>6497.53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1990,22 +2157,22 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1515</v>
+        <v>2266</v>
       </c>
       <c r="H6" t="n">
-        <v>5692.23</v>
+        <v>5857.28</v>
       </c>
       <c r="I6" t="n">
-        <v>853.83</v>
+        <v>878.59</v>
       </c>
       <c r="J6" t="n">
-        <v>6546.06</v>
+        <v>6735.87</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2034,22 +2201,22 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1131</v>
+        <v>2693</v>
       </c>
       <c r="H7" t="n">
-        <v>2807.37</v>
+        <v>4873.16</v>
       </c>
       <c r="I7" t="n">
-        <v>421.11</v>
+        <v>730.97</v>
       </c>
       <c r="J7" t="n">
-        <v>3228.48</v>
+        <v>5604.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2078,22 +2245,22 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2660</v>
+        <v>3070</v>
       </c>
       <c r="H8" t="n">
-        <v>3043.48</v>
+        <v>6368.93</v>
       </c>
       <c r="I8" t="n">
-        <v>456.52</v>
+        <v>955.34</v>
       </c>
       <c r="J8" t="n">
-        <v>3500</v>
+        <v>7324.27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2122,22 +2289,22 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2425</v>
+        <v>2547</v>
       </c>
       <c r="H9" t="n">
-        <v>5371.34</v>
+        <v>6154.52</v>
       </c>
       <c r="I9" t="n">
-        <v>805.7</v>
+        <v>923.1799999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>6177.04</v>
+        <v>7077.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2166,22 +2333,22 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1031</v>
+        <v>3081</v>
       </c>
       <c r="H10" t="n">
-        <v>3208.54</v>
+        <v>2930.89</v>
       </c>
       <c r="I10" t="n">
-        <v>481.28</v>
+        <v>439.63</v>
       </c>
       <c r="J10" t="n">
-        <v>3689.82</v>
+        <v>3370.52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2210,22 +2377,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3039</v>
+        <v>770</v>
       </c>
       <c r="H11" t="n">
-        <v>3818.37</v>
+        <v>4914.72</v>
       </c>
       <c r="I11" t="n">
-        <v>572.76</v>
+        <v>737.21</v>
       </c>
       <c r="J11" t="n">
-        <v>4391.13</v>
+        <v>5651.93</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2254,22 +2421,22 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2206</v>
+        <v>2822</v>
       </c>
       <c r="H12" t="n">
-        <v>3865.17</v>
+        <v>4740.4</v>
       </c>
       <c r="I12" t="n">
-        <v>579.78</v>
+        <v>711.0599999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>4444.95</v>
+        <v>5451.46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2298,22 +2465,22 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1058</v>
+        <v>1406</v>
       </c>
       <c r="H13" t="n">
-        <v>5933.72</v>
+        <v>2933.64</v>
       </c>
       <c r="I13" t="n">
-        <v>890.0599999999999</v>
+        <v>440.05</v>
       </c>
       <c r="J13" t="n">
-        <v>6823.78</v>
+        <v>3373.69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2342,22 +2509,22 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1250</v>
+        <v>1503</v>
       </c>
       <c r="H14" t="n">
-        <v>2916.54</v>
+        <v>5363.33</v>
       </c>
       <c r="I14" t="n">
-        <v>437.48</v>
+        <v>804.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3354.02</v>
+        <v>6167.83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2386,22 +2553,22 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1732</v>
+        <v>1189</v>
       </c>
       <c r="H15" t="n">
-        <v>2659.31</v>
+        <v>5131.68</v>
       </c>
       <c r="I15" t="n">
-        <v>398.9</v>
+        <v>769.75</v>
       </c>
       <c r="J15" t="n">
-        <v>3058.21</v>
+        <v>5901.43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2430,22 +2597,22 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>995</v>
+        <v>2706</v>
       </c>
       <c r="H16" t="n">
-        <v>3037.29</v>
+        <v>6357.5</v>
       </c>
       <c r="I16" t="n">
-        <v>455.59</v>
+        <v>953.62</v>
       </c>
       <c r="J16" t="n">
-        <v>3492.88</v>
+        <v>7311.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2474,16 +2641,148 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2370</v>
+        <v>504</v>
       </c>
       <c r="H17" t="n">
-        <v>5248.94</v>
+        <v>3241.02</v>
       </c>
       <c r="I17" t="n">
-        <v>787.34</v>
+        <v>486.15</v>
       </c>
       <c r="J17" t="n">
-        <v>6036.28</v>
+        <v>3727.17</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hypery</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CN-19900</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SR-4516</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Pietheo Investments</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Harare</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>2012</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4100</v>
+      </c>
+      <c r="I18" t="n">
+        <v>615</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4715</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Surface</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CN-19901</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SR-4517</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TM Retailers</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bulawayo</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>2761</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3050</v>
+      </c>
+      <c r="I19" t="n">
+        <v>457.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3507.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Olivine</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CN-19902</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SR-4518</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PNP Stores</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mutare</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1199</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3720</v>
+      </c>
+      <c r="I20" t="n">
+        <v>558</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4278</v>
       </c>
     </row>
   </sheetData>
@@ -2593,7 +2892,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.4</v>
+        <v>13.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2606,22 +2905,22 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1562.12</v>
+        <v>1270.72</v>
       </c>
       <c r="H2" t="n">
-        <v>390.53</v>
+        <v>317.68</v>
       </c>
       <c r="I2" t="n">
-        <v>390.53</v>
+        <v>317.68</v>
       </c>
       <c r="J2" t="n">
-        <v>390.53</v>
+        <v>317.68</v>
       </c>
       <c r="K2" t="n">
-        <v>390.53</v>
+        <v>317.68</v>
       </c>
       <c r="L2" t="n">
-        <v>1562.12</v>
+        <v>1270.72</v>
       </c>
     </row>
     <row r="3">
@@ -2641,7 +2940,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2654,22 +2953,22 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1631.04</v>
+        <v>1138.32</v>
       </c>
       <c r="H3" t="n">
-        <v>407.76</v>
+        <v>284.58</v>
       </c>
       <c r="I3" t="n">
-        <v>407.76</v>
+        <v>284.58</v>
       </c>
       <c r="J3" t="n">
-        <v>407.76</v>
+        <v>284.58</v>
       </c>
       <c r="K3" t="n">
-        <v>407.76</v>
+        <v>284.58</v>
       </c>
       <c r="L3" t="n">
-        <v>1631.04</v>
+        <v>1138.32</v>
       </c>
     </row>
     <row r="4">
@@ -2689,7 +2988,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2702,22 +3001,22 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1273.24</v>
+        <v>1336.28</v>
       </c>
       <c r="H4" t="n">
-        <v>318.31</v>
+        <v>334.07</v>
       </c>
       <c r="I4" t="n">
-        <v>318.31</v>
+        <v>334.07</v>
       </c>
       <c r="J4" t="n">
-        <v>318.31</v>
+        <v>334.07</v>
       </c>
       <c r="K4" t="n">
-        <v>318.31</v>
+        <v>334.07</v>
       </c>
       <c r="L4" t="n">
-        <v>1273.24</v>
+        <v>1336.28</v>
       </c>
     </row>
     <row r="5">
@@ -2737,7 +3036,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.5</v>
+        <v>7.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2750,22 +3049,22 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1429.52</v>
+        <v>1551.96</v>
       </c>
       <c r="H5" t="n">
-        <v>357.38</v>
+        <v>387.99</v>
       </c>
       <c r="I5" t="n">
-        <v>357.38</v>
+        <v>387.99</v>
       </c>
       <c r="J5" t="n">
-        <v>357.38</v>
+        <v>387.99</v>
       </c>
       <c r="K5" t="n">
-        <v>357.38</v>
+        <v>387.99</v>
       </c>
       <c r="L5" t="n">
-        <v>1429.52</v>
+        <v>1551.96</v>
       </c>
     </row>
     <row r="6">
@@ -2785,7 +3084,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.8</v>
+        <v>13.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2798,22 +3097,22 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1149.04</v>
+        <v>1592.16</v>
       </c>
       <c r="H6" t="n">
-        <v>287.26</v>
+        <v>398.04</v>
       </c>
       <c r="I6" t="n">
-        <v>287.26</v>
+        <v>398.04</v>
       </c>
       <c r="J6" t="n">
-        <v>287.26</v>
+        <v>398.04</v>
       </c>
       <c r="K6" t="n">
-        <v>287.26</v>
+        <v>398.04</v>
       </c>
       <c r="L6" t="n">
-        <v>1149.04</v>
+        <v>1592.16</v>
       </c>
     </row>
     <row r="7">
@@ -2833,7 +3132,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2846,22 +3145,22 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1273.76</v>
+        <v>1096.56</v>
       </c>
       <c r="H7" t="n">
-        <v>318.44</v>
+        <v>274.14</v>
       </c>
       <c r="I7" t="n">
-        <v>318.44</v>
+        <v>274.14</v>
       </c>
       <c r="J7" t="n">
-        <v>318.44</v>
+        <v>274.14</v>
       </c>
       <c r="K7" t="n">
-        <v>318.44</v>
+        <v>274.14</v>
       </c>
       <c r="L7" t="n">
-        <v>1273.76</v>
+        <v>1096.56</v>
       </c>
     </row>
     <row r="8">
@@ -2881,7 +3180,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2894,22 +3193,22 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1477.88</v>
+        <v>1476.12</v>
       </c>
       <c r="H8" t="n">
-        <v>369.47</v>
+        <v>369.03</v>
       </c>
       <c r="I8" t="n">
-        <v>369.47</v>
+        <v>369.03</v>
       </c>
       <c r="J8" t="n">
-        <v>369.47</v>
+        <v>369.03</v>
       </c>
       <c r="K8" t="n">
-        <v>369.47</v>
+        <v>369.03</v>
       </c>
       <c r="L8" t="n">
-        <v>1477.88</v>
+        <v>1476.12</v>
       </c>
     </row>
     <row r="9">
@@ -2929,7 +3228,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.9</v>
+        <v>7.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2942,22 +3241,22 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1101.64</v>
+        <v>1271.96</v>
       </c>
       <c r="H9" t="n">
-        <v>275.41</v>
+        <v>317.99</v>
       </c>
       <c r="I9" t="n">
-        <v>275.41</v>
+        <v>317.99</v>
       </c>
       <c r="J9" t="n">
-        <v>275.41</v>
+        <v>317.99</v>
       </c>
       <c r="K9" t="n">
-        <v>275.41</v>
+        <v>317.99</v>
       </c>
       <c r="L9" t="n">
-        <v>1101.64</v>
+        <v>1271.96</v>
       </c>
     </row>
     <row r="10">
@@ -2977,7 +3276,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2990,22 +3289,22 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1326.36</v>
+        <v>1293.48</v>
       </c>
       <c r="H10" t="n">
-        <v>331.59</v>
+        <v>323.37</v>
       </c>
       <c r="I10" t="n">
-        <v>331.59</v>
+        <v>323.37</v>
       </c>
       <c r="J10" t="n">
-        <v>331.59</v>
+        <v>323.37</v>
       </c>
       <c r="K10" t="n">
-        <v>331.59</v>
+        <v>323.37</v>
       </c>
       <c r="L10" t="n">
-        <v>1326.36</v>
+        <v>1293.48</v>
       </c>
     </row>
     <row r="11">
@@ -3025,7 +3324,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.9</v>
+        <v>5.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3038,22 +3337,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1369.04</v>
+        <v>1005.8</v>
       </c>
       <c r="H11" t="n">
-        <v>342.26</v>
+        <v>251.45</v>
       </c>
       <c r="I11" t="n">
-        <v>342.26</v>
+        <v>251.45</v>
       </c>
       <c r="J11" t="n">
-        <v>342.26</v>
+        <v>251.45</v>
       </c>
       <c r="K11" t="n">
-        <v>342.26</v>
+        <v>251.45</v>
       </c>
       <c r="L11" t="n">
-        <v>1369.04</v>
+        <v>1005.8</v>
       </c>
     </row>
   </sheetData>
@@ -3067,7 +3366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3131,7 +3430,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>04.10.26</t>
+          <t>24.09.26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3155,7 +3454,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10674</v>
+        <v>7388</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3168,13 +3467,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>662.99</v>
+        <v>462.49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17.10.26</t>
+          <t>05.08.26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3198,7 +3497,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7033</v>
+        <v>3227</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -3211,13 +3510,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>685.76</v>
+        <v>124.06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17.10.26</t>
+          <t>24.09.26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3241,7 +3540,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6910</v>
+        <v>4816</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -3254,13 +3553,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>235.11</v>
+        <v>482.48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11.10.26</t>
+          <t>26.09.26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3284,7 +3583,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>13111</v>
+        <v>10547</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3297,13 +3596,13 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>381.48</v>
+        <v>521.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11.10.26</t>
+          <t>27.09.26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3327,7 +3626,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13447</v>
+        <v>5538</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3340,13 +3639,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>485.47</v>
+        <v>499.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15.10.26</t>
+          <t>26.08.26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3370,7 +3669,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10527</v>
+        <v>14167</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3383,13 +3682,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>360.91</v>
+        <v>532.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10.10.26</t>
+          <t>26.09.26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3413,7 +3712,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>8948</v>
+        <v>11262</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -3426,13 +3725,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>646.65</v>
+        <v>130.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10.10.26</t>
+          <t>14.09.26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3456,7 +3755,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>12515</v>
+        <v>8751</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3469,13 +3768,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>336.12</v>
+        <v>622.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18.10.26</t>
+          <t>24.09.26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3499,7 +3798,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4546</v>
+        <v>11280</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3512,13 +3811,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>201.87</v>
+        <v>634.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21.10.26</t>
+          <t>16.08.26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3542,7 +3841,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6188</v>
+        <v>8423</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3555,13 +3854,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>212.64</v>
+        <v>674.46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13.10.26</t>
+          <t>22.09.26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3585,7 +3884,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3295</v>
+        <v>5660</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3598,13 +3897,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>478.72</v>
+        <v>362.32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07.10.26</t>
+          <t>08.08.26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3628,7 +3927,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4829</v>
+        <v>12056</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3641,13 +3940,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>453.57</v>
+        <v>318.61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12.10.26</t>
+          <t>26.09.26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3671,7 +3970,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7376</v>
+        <v>6960</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3684,7 +3983,93 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>667.28</v>
+        <v>181.96</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>28.09.26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Olivine</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bhola Enterprises</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AMARAS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>INV-7300</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>8800</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ACD2345</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kwekwe</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>27.09.26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hypery</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PNP Stores</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>WILLAND</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>INV-7301</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AHE0473</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Chitungwiza</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>298.5</v>
       </c>
     </row>
   </sheetData>
